--- a/AAISM TOC.xlsx
+++ b/AAISM TOC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhavnaw\Downloads\ISACA Advanced in AI Security Management (AAISM)\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628D385D-18EF-4BA7-8947-44222B5BFFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7FBD09-08D1-4024-BC96-EDC9B8D7D623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <definedName name="In_Process">#REF!</definedName>
     <definedName name="STATUS">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -4858,6 +4858,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="76027dd9-77cd-484f-b6db-8bbe1351c2b5">
@@ -4867,15 +4876,6 @@
     <Comments xmlns="76027dd9-77cd-484f-b6db-8bbe1351c2b5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5153,6 +5153,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A42F3CFC-C897-4556-A913-297D413ED195}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F00D1D03-D728-4FCC-8D12-B8950FAF17A2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -5166,14 +5174,6 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A42F3CFC-C897-4556-A913-297D413ED195}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
